--- a/models/Three_Statement_Model_SaaS_HubSpot.xlsx
+++ b/models/Three_Statement_Model_SaaS_HubSpot.xlsx
@@ -1119,7 +1119,7 @@
     <t xml:space="preserve">Free cash flow margin — FY2025 %</t>
   </si>
   <si>
-    <t xml:space="preserve">18% FCF margin (after capitalized software) is just below the 21% median — the leverage story is still mid-flight.</t>
+    <t xml:space="preserve">18% FCF margin (after capitalized software) is just below the 21% median; operating leverage is still building.</t>
   </si>
   <si>
     <t xml:space="preserve">Rule of 40 (growth + FCF margin)</t>

--- a/models/Three_Statement_Model_SaaS_HubSpot.xlsx
+++ b/models/Three_Statement_Model_SaaS_HubSpot.xlsx
@@ -31,12 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="478">
   <si>
     <t xml:space="preserve">HUBSPOT, INC.  (NYSE: HUBS)</t>
   </si>
   <si>
-    <t xml:space="preserve">Three-Statement Financial Model — SaaS — Customer Platform (CRM, Marketing, Sales &amp; Service)</t>
+    <t xml:space="preserve">Three-Statement Financial Model; SaaS; Customer Platform (CRM, Marketing, Sales &amp; Service)</t>
   </si>
   <si>
     <t xml:space="preserve">Integrated Income Statement · Balance Sheet · Cash Flow · driver-based forecast · regional scenarios · live market data</t>
@@ -63,16 +63,16 @@
     <t xml:space="preserve">HOW TO USE THIS MODEL</t>
   </si>
   <si>
-    <t xml:space="preserve">1.  Start on the Revenue Drivers and Assumptions tabs — every blue cell is an input; yellow cells are the key levers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.  Flip the scenario selector on Regional Breakdown (1 = Standard · 2 = Best Case · 3 = Low Case) — the whole model re-runs, including EPS, cash and the benchmarking tab.</t>
+    <t xml:space="preserve">1.  Start on the Revenue Drivers and Assumptions tabs; every blue cell is an input; yellow cells are the key levers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.  Flip the scenario selector on Regional Breakdown (1 = Standard · 2 = Best Case · 3 = Low Case); the whole model re-runs, including EPS, cash and the benchmarking tab.</t>
   </si>
   <si>
     <t xml:space="preserve">3.  Check Budget vs Actual for FY2025 performance vs guidance; rows over the 10% threshold flag automatically.</t>
   </si>
   <si>
-    <t xml:space="preserve">4.  Keep market data current: run refresh_market_data.py in this folder (or use the dashboard ⟳ button) — stamps update on Market Inputs and the refresh is logged in Version History.</t>
+    <t xml:space="preserve">4.  Keep market data current: run refresh_market_data.py in this folder (or use the dashboard ⟳ button); stamps update on Market Inputs and the refresh is logged in Version History.</t>
   </si>
   <si>
     <t xml:space="preserve">5.  For a browser walkthrough or a one-page memo, open Finance_AI_Dashboard.html and use Export memo (PDF).</t>
@@ -93,19 +93,19 @@
     <t xml:space="preserve">COLOR CONVENTIONS</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue — hardcoded input (historical figures as reported; forecast assumptions)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black — formula / calculation          Green — direct link to another sheet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow fill — key assumption levers to flex</t>
+    <t xml:space="preserve">Blue = hardcoded input (historical figures as reported; forecast assumptions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Black = formula / calculation          Green = direct link to another sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yellow fill = key assumption levers to flex</t>
   </si>
   <si>
     <t xml:space="preserve">Every data input is cited on the Sources tab, with links and last-updated dates.</t>
   </si>
   <si>
-    <t xml:space="preserve">HubSpot, Inc. — Forecast Assumptions</t>
+    <t xml:space="preserve">HubSpot, Inc.; Forecast Assumptions</t>
   </si>
   <si>
     <t xml:space="preserve">(USD in thousands, except per-share amounts) · FY2023A–FY2025A per SEC filings · FY2026E–FY2030E forecast</t>
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Income statement drivers</t>
   </si>
   <si>
-    <t xml:space="preserve">    Subscription revenue growth % — OUTPUT (driven by Revenue Drivers tab)</t>
+    <t xml:space="preserve">    Subscription revenue growth %; OUTPUT (driven by Revenue Drivers tab)</t>
   </si>
   <si>
     <t xml:space="preserve">Seat + AI-credit expansion moderates from FY25's 19.2%</t>
@@ -192,7 +192,7 @@
     <t xml:space="preserve">Balance sheet drivers</t>
   </si>
   <si>
-    <t xml:space="preserve">    Accounts receivable — days sales outstanding</t>
+    <t xml:space="preserve">    Accounts receivable · days sales outstanding</t>
   </si>
   <si>
     <t xml:space="preserve">    Deferred commissions (current) % of revenue</t>
@@ -255,7 +255,7 @@
     <t xml:space="preserve">Investments, leases, goodwill and intangibles held flat in the forecast; 2025 convertible notes were repaid at maturity.</t>
   </si>
   <si>
-    <t xml:space="preserve">HubSpot, Inc. — Revenue Drivers (SaaS)</t>
+    <t xml:space="preserve">HubSpot, Inc.; Revenue Drivers (SaaS)</t>
   </si>
   <si>
     <t xml:space="preserve">SaaS unit-economics build (USD in thousands unless noted) · drives Subscription revenue on the Income Statement</t>
@@ -264,7 +264,7 @@
     <t xml:space="preserve">Customer roll-forward</t>
   </si>
   <si>
-    <t xml:space="preserve">    Customers — beginning of period</t>
+    <t xml:space="preserve">    Customers, beginning of period</t>
   </si>
   <si>
     <t xml:space="preserve">    New customers added (new-business S&amp;M ÷ CAC)</t>
@@ -273,7 +273,7 @@
     <t xml:space="preserve">    Less: customers churned</t>
   </si>
   <si>
-    <t xml:space="preserve">    Customers — end of period</t>
+    <t xml:space="preserve">    Customers · end of period</t>
   </si>
   <si>
     <t xml:space="preserve">    Average customers</t>
@@ -285,7 +285,7 @@
     <t xml:space="preserve">    Annual logo churn rate %</t>
   </si>
   <si>
-    <t xml:space="preserve">    Customer acquisition cost — CAC ($000s / customer)</t>
+    <t xml:space="preserve">    Customer acquisition cost · CAC ($000s / customer)</t>
   </si>
   <si>
     <t xml:space="preserve">    % of prior-year S&amp;M deployed on new business</t>
@@ -294,7 +294,7 @@
     <t xml:space="preserve">    New-business S&amp;M budget ($000s, lagged one year)</t>
   </si>
   <si>
-    <t xml:space="preserve">    First-year ARPC — new customers ($000s)</t>
+    <t xml:space="preserve">    First-year ARPC · new customers ($000s)</t>
   </si>
   <si>
     <t xml:space="preserve">    Net revenue retention (NRR) %</t>
@@ -336,10 +336,10 @@
     <t xml:space="preserve">New adds are funded from PRIOR-year S&amp;M (lagged) to avoid a circular reference with current-year revenue.</t>
   </si>
   <si>
-    <t xml:space="preserve">CAC and churn are blended estimates (not company-disclosed) — flex the blue inputs to test unit-economics scenarios.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HubSpot, Inc. — Regional Breakdown &amp; Scenarios</t>
+    <t xml:space="preserve">CAC and churn are blended estimates (not company-disclosed); flex the blue inputs to test unit-economics scenarios.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HubSpot, Inc.; Regional Breakdown &amp; Scenarios</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue, growth and customers by region (USD in thousands unless noted) · regional scenario toggle feeds the Income Statement · base = total revenue</t>
@@ -366,22 +366,22 @@
     <t xml:space="preserve">BASE TOTAL REVENUE BY REGION ($000s)</t>
   </si>
   <si>
-    <t xml:space="preserve">    Professional services &amp; other revenue — base path</t>
+    <t xml:space="preserve">    Professional services &amp; other revenue · base path</t>
   </si>
   <si>
     <t xml:space="preserve">    Base total revenue before regional split</t>
   </si>
   <si>
-    <t xml:space="preserve">    North America — base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Europe — base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Asia Pacific — base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Other / rest of world — base</t>
+    <t xml:space="preserve">    North America · base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Europe · base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Asia Pacific · base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Other / rest of world · base</t>
   </si>
   <si>
     <t xml:space="preserve">    Total base (sum of regions)</t>
@@ -402,40 +402,40 @@
     <t xml:space="preserve">SCENARIO GROWTH DELTAS (added to base regional growth)</t>
   </si>
   <si>
-    <t xml:space="preserve">    Best Case — North America</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Best Case — Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Best Case — Asia Pacific</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Low Case — North America</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Low Case — Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Low Case — Asia Pacific</t>
+    <t xml:space="preserve">    Best Case · North America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Best Case · Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Best Case · Asia Pacific</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Low Case · North America</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Low Case · Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Low Case · Asia Pacific</t>
   </si>
   <si>
     <t xml:space="preserve">SCENARIO TOTAL REVENUE BY REGION ($000s)</t>
   </si>
   <si>
-    <t xml:space="preserve">    North America — scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Europe — scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Asia Pacific — scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Other / rest of world — scenario (no delta)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL — SCENARIO ($000s)</t>
+    <t xml:space="preserve">    North America · scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Europe · scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Asia Pacific · scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Other / rest of world · scenario (no delta)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL · SCENARIO ($000s)</t>
   </si>
   <si>
     <t xml:space="preserve">    Scenario total growth %</t>
@@ -450,13 +450,13 @@
     <t xml:space="preserve">SCENARIO IMPACT DASHBOARD (flips with the selector)</t>
   </si>
   <si>
-    <t xml:space="preserve">    Net income — scenario ($000s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Diluted EPS — scenario ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Ending cash — scenario ($000s)</t>
+    <t xml:space="preserve">    Net income · scenario ($000s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Diluted EPS · scenario ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Ending cash · scenario ($000s)</t>
   </si>
   <si>
     <t xml:space="preserve">    Revenue CAGR FY2025A → FY2030E (scenario)</t>
@@ -480,16 +480,16 @@
     <t xml:space="preserve">    Other customer mix % (balancing)</t>
   </si>
   <si>
-    <t xml:space="preserve">    North America — customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Europe — customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Asia Pacific — customers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Other — customers</t>
+    <t xml:space="preserve">    North America · customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Europe · customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Asia Pacific · customers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Other · customers</t>
   </si>
   <si>
     <t xml:space="preserve">Check: regional mix sums to 100% (must be 0)</t>
@@ -504,10 +504,10 @@
     <t xml:space="preserve">•  The scenario scaling factor multiplies both subscription and services revenue on the Income Statement, so all downstream statements flex with the toggle. New-customer adds also respond (they are funded from prior-year S&amp;M).</t>
   </si>
   <si>
-    <t xml:space="preserve">•  Customer regional mix is an estimate — HubSpot discloses customer counts in total (288,706 at FY25) but not by region; international customers skew higher than revenue mix due to lower ARPC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HubSpot, Inc. — Income Statement</t>
+    <t xml:space="preserve">•  Customer regional mix is an estimate; HubSpot discloses customer counts in total (288,706 at FY25) but not by region; international customers skew higher than revenue mix due to lower ARPC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HubSpot, Inc.; Income Statement</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue</t>
@@ -528,10 +528,10 @@
     <t xml:space="preserve">Cost of revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">    Cost of revenue — subscription</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    Cost of revenue — professional services and other</t>
+    <t xml:space="preserve">    Cost of revenue · subscription</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Cost of revenue · professional services and other</t>
   </si>
   <si>
     <t xml:space="preserve">Total cost of revenue</t>
@@ -597,7 +597,7 @@
     <t xml:space="preserve">Memo: amortization of capitalized software</t>
   </si>
   <si>
-    <t xml:space="preserve">HubSpot, Inc. — Balance Sheet</t>
+    <t xml:space="preserve">HubSpot, Inc.; Balance Sheet</t>
   </si>
   <si>
     <t xml:space="preserve">Assets</t>
@@ -723,7 +723,7 @@
     <t xml:space="preserve">Must be zero in every period</t>
   </si>
   <si>
-    <t xml:space="preserve">HubSpot, Inc. — Statement of Cash Flows</t>
+    <t xml:space="preserve">HubSpot, Inc.; Statement of Cash Flows</t>
   </si>
   <si>
     <t xml:space="preserve">Operating activities</t>
@@ -816,10 +816,10 @@
     <t xml:space="preserve">Net increase in cash</t>
   </si>
   <si>
-    <t xml:space="preserve">    Cash, equivalents and restricted cash — beginning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash, equivalents and restricted cash — ending</t>
+    <t xml:space="preserve">    Cash, equivalents and restricted cash, beginning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash, equivalents and restricted cash, ending</t>
   </si>
   <si>
     <t xml:space="preserve">    Less: restricted cash</t>
@@ -831,7 +831,7 @@
     <t xml:space="preserve">Links to cash on the balance sheet</t>
   </si>
   <si>
-    <t xml:space="preserve">HubSpot, Inc. — Budget vs Actual Variance</t>
+    <t xml:space="preserve">HubSpot, Inc.; Budget vs Actual Variance</t>
   </si>
   <si>
     <t xml:space="preserve">FY2025 actual vs FY2025 budget (USD in thousands, except per-share) · Budget seeded from company guidance where published; all budget cells editable</t>
@@ -870,7 +870,7 @@
     <t xml:space="preserve">Company FY25 guidance (Feb 12, 2025): $2,985–2,995M</t>
   </si>
   <si>
-    <t xml:space="preserve">Placeholder — replace with your budget</t>
+    <t xml:space="preserve">Placeholder · replace with your budget</t>
   </si>
   <si>
     <t xml:space="preserve">Income (loss) from operations (GAAP)</t>
@@ -900,7 +900,7 @@
     <t xml:space="preserve">•  Budget column is seeded with the midpoint of company guidance issued at the start of FY2025 where published (see Budget source).</t>
   </si>
   <si>
-    <t xml:space="preserve">•  Rows marked "Placeholder" carry illustrative budgets — overwrite them, or type your own number in the yellow Override column (it takes precedence).</t>
+    <t xml:space="preserve">•  Rows marked "Placeholder" carry illustrative budgets; overwrite them, or type your own number in the yellow Override column (it takes precedence).</t>
   </si>
   <si>
     <t xml:space="preserve">•  GAAP actuals pull live from the statement tabs (green); non-GAAP actuals are per the company's Q4 FY2025 earnings release.</t>
@@ -909,10 +909,10 @@
     <t xml:space="preserve">•  Rows turn red automatically when |Variance %| exceeds the threshold in B4.</t>
   </si>
   <si>
-    <t xml:space="preserve">HubSpot, Inc. — Market Inputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snapshot as of market close July 17, 2026 · All values are inputs (blue) — see REFRESH section to wire live updates</t>
+    <t xml:space="preserve">HubSpot, Inc.; Market Inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snapshot as of market close July 17, 2026 · All values are inputs (blue); see REFRESH section to wire live updates</t>
   </si>
   <si>
     <t xml:space="preserve">Data as of:</t>
@@ -960,7 +960,7 @@
     <t xml:space="preserve">30-year Treasury</t>
   </si>
   <si>
-    <t xml:space="preserve">EQUITY MARKET DATA — PEER SET</t>
+    <t xml:space="preserve">EQUITY MARKET DATA: PEER SET</t>
   </si>
   <si>
     <t xml:space="preserve">PLTR</t>
@@ -999,7 +999,7 @@
     <t xml:space="preserve">Selected EV / Revenue multiple (x)</t>
   </si>
   <si>
-    <t xml:space="preserve">Defaults to this company's current multiple — flex it or use a peer's</t>
+    <t xml:space="preserve">Defaults to this company's current multiple; flex it or use a peer's</t>
   </si>
   <si>
     <t xml:space="preserve">Model FY2026E revenue ($000s)</t>
@@ -1032,7 +1032,7 @@
     <t xml:space="preserve">Implied premium / (discount) to current market cap</t>
   </si>
   <si>
-    <t xml:space="preserve">REFRESH — MAKE THIS TAB LIVE (one-time setup, ~2 minutes in Excel)</t>
+    <t xml:space="preserve">REFRESH: MAKE THIS TAB LIVE (one-time setup, ~2 minutes in Excel)</t>
   </si>
   <si>
     <t xml:space="preserve">1.  Excel ▸ Data ▸ Get Data (Power Query) ▸ From Other Sources ▸ From Web.</t>
@@ -1044,19 +1044,19 @@
     <t xml:space="preserve">3.  Load the query to a new sheet; point the blue rate cells above at the latest row (e.g. =INDEX(...)).</t>
   </si>
   <si>
-    <t xml:space="preserve">4.  Share prices (JSON):  https://query1.finance.yahoo.com/v8/finance/chart/HUBS   — Power Query ▸ From Web, drill to chart.result.meta.regularMarketPrice.</t>
+    <t xml:space="preserve">4.  Share prices (JSON):  https://query1.finance.yahoo.com/v8/finance/chart/HUBS  ; Power Query ▸ From Web, drill to chart.result.meta.regularMarketPrice.</t>
   </si>
   <si>
     <t xml:space="preserve">5.  After setup, Data ▸ Refresh All re-pulls everything with one click.</t>
   </si>
   <si>
-    <t xml:space="preserve">6.  Until then this tab is a dated snapshot (see B4) — or ask Claude to refresh the numbers any time.</t>
+    <t xml:space="preserve">6.  Until then this tab is a dated snapshot (see B4); or ask Claude to refresh the numbers any time.</t>
   </si>
   <si>
     <t xml:space="preserve">Sources for this snapshot: Fed H.15 (Jul 17, 2026), NY Fed SOFR, stockanalysis.com / S&amp;P Global (Jul 17–19, 2026).</t>
   </si>
   <si>
-    <t xml:space="preserve">HubSpot, Inc. — Competitor Benchmarking</t>
+    <t xml:space="preserve">HubSpot, Inc.; Competitor Benchmarking</t>
   </si>
   <si>
     <t xml:space="preserve">Company column pulls live from this model (FY2025 actuals; FY2026E is scenario-aware) · comps per latest reported fiscal year, valuations as of July 17–20, 2026 · industry benchmarks: Clouded Judgement SaaS medians (7/10/26) and US bank norms</t>
@@ -1089,34 +1089,34 @@
     <t xml:space="preserve">HubSpot sits between the mega-platform (CRM, 13x its size) and the SMB challenger (MNDY, 40% its size).</t>
   </si>
   <si>
-    <t xml:space="preserve">Revenue growth — FY2025 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19% growth beats the 13% SaaS median and CRM (10%), trails MNDY (27%) — solidly in the mid-growth bucket.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue growth — FY2026E (model, scenario-aware) %</t>
+    <t xml:space="preserve">Revenue growth · FY2025 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19% growth beats the 13% SaaS median and CRM (10%), trails MNDY (27%); solidly in the mid-growth bucket.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue growth · FY2026E (model, scenario-aware) %</t>
   </si>
   <si>
     <t xml:space="preserve">n/a</t>
   </si>
   <si>
-    <t xml:space="preserve">Model FY26E growth (scenario-aware) of ~18% assumes NRR recovery plus steady customer adds — see Revenue Drivers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAAP gross margin — FY2025 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84% GAAP gross margin is top-decile — above CRM and the median, just below MNDY's 89%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAAP operating margin — FY2025 %</t>
+    <t xml:space="preserve">Model FY26E growth (scenario-aware) of ~18% assumes NRR recovery plus steady customer adds; see Revenue Drivers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAAP gross margin · FY2025 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84% GAAP gross margin is top-decile; above CRM and the median, just below MNDY's 89%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAAP operating margin · FY2025 %</t>
   </si>
   <si>
     <t xml:space="preserve">GAAP operating margin ~0% vs CRM's 20% reflects heavy SBC; non-GAAP operating margin was 18.6% in FY25.</t>
   </si>
   <si>
-    <t xml:space="preserve">Free cash flow margin — FY2025 %</t>
+    <t xml:space="preserve">Free cash flow margin · FY2025 %</t>
   </si>
   <si>
     <t xml:space="preserve">18% FCF margin (after capitalized software) is just below the 21% median; operating leverage is still building.</t>
@@ -1131,7 +1131,7 @@
     <t xml:space="preserve">EV / Revenue (TTM) (x)</t>
   </si>
   <si>
-    <t xml:space="preserve">At 3.0x TTM revenue HubSpot trades BELOW the 5.4x mid-growth bucket median — the market is pricing it like a low-growth asset despite 19% growth.</t>
+    <t xml:space="preserve">At 3.0x TTM revenue HubSpot trades BELOW the 5.4x mid-growth bucket median; the market is pricing it like a low-growth asset despite 19% growth.</t>
   </si>
   <si>
     <t xml:space="preserve">Forward P/E (x, non-GAAP consensus basis)</t>
@@ -1140,7 +1140,7 @@
     <t xml:space="preserve">~21x S&amp;P 500</t>
   </si>
   <si>
-    <t xml:space="preserve">16x forward earnings (non-GAAP basis) is a modest premium to CRM (12x) — cheap relative to its history and growth.</t>
+    <t xml:space="preserve">16x forward earnings (non-GAAP basis) is a modest premium to CRM (12x); cheap relative to its history and growth.</t>
   </si>
   <si>
     <t xml:space="preserve">INDUSTRY BENCHMARK NOTES</t>
@@ -1152,10 +1152,10 @@
     <t xml:space="preserve">•  Rule of 40 = revenue growth % + FCF margin % ≥ 40% is the standard bar for a healthy software business.</t>
   </si>
   <si>
-    <t xml:space="preserve">TAKEAWAYS — WHAT THIS COMPARISON MEANS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•  HubSpot's operating metrics (19% growth, 84% gross margin, ~38% Rule of 40) screen mid-pack-or-better, but its 3.0x EV/revenue sits below the mid-growth SaaS bucket median of 5.4x — a potential re-rating gap.</t>
+    <t xml:space="preserve">TAKEAWAYS: WHAT THIS COMPARISON MEANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">•  HubSpot's operating metrics (19% growth, 84% gross margin, ~38% Rule of 40) screen mid-pack-or-better, but its 3.0x EV/revenue sits below the mid-growth SaaS bucket median of 5.4x; a potential re-rating gap.</t>
   </si>
   <si>
     <t xml:space="preserve">•  The GAAP/non-GAAP spread is the story: ~0% GAAP operating margin vs 18.6% non-GAAP is almost entirely stock-based comp (~17% of revenue in the model assumptions).</t>
@@ -1167,7 +1167,7 @@
     <t xml:space="preserve">Sources: company Q4/FY earnings releases and 10-Ks (SEC EDGAR); stockanalysis.com / S&amp;P Global valuations Jul 17–20, 2026; cloudedjudgement.substack.com 7/10/26; multiples.vc Jul 2026. Comp forward P/Es are consensus (non-GAAP) based.</t>
   </si>
   <si>
-    <t xml:space="preserve">HubSpot, Inc. — Version History</t>
+    <t xml:space="preserve">HubSpot, Inc.; Version History</t>
   </si>
   <si>
     <t xml:space="preserve">Log of every assumptions refresh: what changed, when, and why. Add a new row each time inputs are updated.</t>
@@ -1200,7 +1200,7 @@
     <t xml:space="preserve">Initial build: FY2023–FY2025 actuals per SEC filings; FY2026–FY2030 top-down forecast; Assumptions, Income Statement, Balance Sheet, Cash Flow and Cover with sheet links.</t>
   </si>
   <si>
-    <t xml:space="preserve">Portfolio work sample — integrated three-statement model with balance and cash tie-out checks.</t>
+    <t xml:space="preserve">Portfolio work sample: integrated three-statement model with balance and cash tie-out checks.</t>
   </si>
   <si>
     <t xml:space="preserve">1.1</t>
@@ -1221,7 +1221,7 @@
     <t xml:space="preserve">Rebuilt revenue as a bottoms-up Revenue Drivers tab (customer roll-forward (CAC/churn), NRR expansion, first-year ARPC); superseded top-down assumption rows relabeled as OUTPUT.</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit-economics realism — forecast driven by operating metrics rather than a single growth rate.</t>
+    <t xml:space="preserve">Unit-economics realism: forecast driven by operating metrics rather than a single growth rate.</t>
   </si>
   <si>
     <t xml:space="preserve">1.3</t>
@@ -1239,7 +1239,7 @@
     <t xml:space="preserve">Added Competitor Benchmarking tab vs Salesforce and monday.com + SaaS industry medians; company column pulls live from the model with interpretation and takeaways.</t>
   </si>
   <si>
-    <t xml:space="preserve">Relative context — absolute metrics only matter versus peers and industry medians.</t>
+    <t xml:space="preserve">Relative context: absolute metrics only matter versus peers and industry medians.</t>
   </si>
   <si>
     <t xml:space="preserve">1.5</t>
@@ -1257,7 +1257,7 @@
     <t xml:space="preserve">Added this Version History tab.</t>
   </si>
   <si>
-    <t xml:space="preserve">Change auditability — every future assumptions refresh gets logged here.</t>
+    <t xml:space="preserve">Change auditability: every future assumptions refresh gets logged here.</t>
   </si>
   <si>
     <t xml:space="preserve">1.7</t>
@@ -1275,13 +1275,22 @@
     <t xml:space="preserve">Applied workbook protection: all formulas, labels and structure locked with a password on every tab; blue/yellow input cells (assumptions, scenario selector, budget overrides) remain editable so the model stays interactive.</t>
   </si>
   <si>
-    <t xml:space="preserve">Distribution protection — models are downloadable from the public portfolio site; viewers can flex inputs but cannot alter or break the model.</t>
+    <t xml:space="preserve">Distribution protection: models are downloadable from the public portfolio site; viewers can flex inputs but cannot alter or break the model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copy edit across all tabs: punctuation and separator cleanup for a natural reading style; no numbers or formulas changed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Readability pass ahead of public distribution.</t>
   </si>
   <si>
     <t xml:space="preserve">How to log a refresh: add a row (yellow cells above are ready) with the new version number, date, your name, the cells/tabs you changed (e.g. "Assumptions F7: FY27 revenue growth 45% → 40% after Q1 FY27 print"), and the reason. Keep one row per refresh so the audit trail stays readable.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hubspot, Inc. — Data Sources &amp; Citations</t>
+    <t xml:space="preserve">Hubspot, Inc.; Data Sources &amp; Citations</t>
   </si>
   <si>
     <t xml:space="preserve">Every input in this model, where it comes from, and how current it is. Click "Open ↗" for the underlying source. Refresh stamps also appear on Market Inputs; refreshes are logged in Version History.</t>
@@ -1317,7 +1326,7 @@
     <t xml:space="preserve">HubSpot Q4 FY2025 earnings release, 8-K Ex. 99.1, filed Feb 11, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Static actuals — restate on next annual filing</t>
+    <t xml:space="preserve">Static actuals · restate on next annual filing</t>
   </si>
   <si>
     <t xml:space="preserve">FY2023 financial statements (as revised)</t>
@@ -1338,7 +1347,7 @@
     <t xml:space="preserve">FY2025 Form 10-K, geographic data note, filed Feb 11, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Static — update on next 10-K</t>
+    <t xml:space="preserve">Static · update on next 10-K</t>
   </si>
   <si>
     <t xml:space="preserve">Customer counts (205,091 → 288,706), ARPC, net revenue retention</t>
@@ -1350,7 +1359,7 @@
     <t xml:space="preserve">Q4 FY2023–FY2025 releases; NRR ~101.8% (FY24) / ~103.5% (FY25) per earnings calls</t>
   </si>
   <si>
-    <t xml:space="preserve">Static — update quarterly; CAC and churn are analyst estimates</t>
+    <t xml:space="preserve">Static · update quarterly; CAC and churn are analyst estimates</t>
   </si>
   <si>
     <t xml:space="preserve">GUIDANCE &amp; BUDGET</t>
@@ -1365,7 +1374,7 @@
     <t xml:space="preserve">Issued with Q4 FY2024 release, Feb 12, 2025 ($2,985–2,995M revenue)</t>
   </si>
   <si>
-    <t xml:space="preserve">Static — replace with FY2026 guidance next cycle</t>
+    <t xml:space="preserve">Static · replace with FY2026 guidance next cycle</t>
   </si>
   <si>
     <t xml:space="preserve">MARKET DATA</t>
@@ -1401,7 +1410,7 @@
     <t xml:space="preserve">Market Inputs · Competitor Benchmarking</t>
   </si>
   <si>
-    <t xml:space="preserve">stockanalysis.com (HUBS) — data: S&amp;P Global Market Intelligence, close Jul 17, 2026</t>
+    <t xml:space="preserve">stockanalysis.com (HUBS); data: S&amp;P Global Market Intelligence, close Jul 17, 2026</t>
   </si>
   <si>
     <t xml:space="preserve">refresh_market_data.py scales by live price ratio</t>
@@ -1410,7 +1419,7 @@
     <t xml:space="preserve">VALUATION &amp; INDUSTRY BENCHMARKS</t>
   </si>
   <si>
-    <t xml:space="preserve">Comp fundamentals — Salesforce (FY ended 1/26)</t>
+    <t xml:space="preserve">Comp fundamentals · Salesforce (FY ended 1/26)</t>
   </si>
   <si>
     <t xml:space="preserve">Competitor Benchmarking</t>
@@ -1419,10 +1428,10 @@
     <t xml:space="preserve">Salesforce Q4 FY2026 results, Feb 25, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Static — update after comp earnings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comp fundamentals — monday.com (FY2025)</t>
+    <t xml:space="preserve">Static · update after comp earnings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comp fundamentals · monday.com (FY2025)</t>
   </si>
   <si>
     <t xml:space="preserve">monday.com Q4/FY2025 6-K press release, Feb 9, 2026</t>
@@ -1437,7 +1446,7 @@
     <t xml:space="preserve">2026-07-10</t>
   </si>
   <si>
-    <t xml:space="preserve">Manual — ask Claude to refresh</t>
+    <t xml:space="preserve">Manual · ask Claude to refresh</t>
   </si>
   <si>
     <t xml:space="preserve">FORECAST ASSUMPTIONS</t>
@@ -1455,7 +1464,7 @@
     <t xml:space="preserve">Every change is logged on the Version History tab</t>
   </si>
   <si>
-    <t xml:space="preserve">Conventions: "Static actuals" never change once filed (restated only if the company restates). Market data carries dual stamps — "Data as of" (the market close the values describe) and "Last refreshed" (when the file was last updated). Analyst assumptions are the author's judgment; the Version History tab is the audit trail.</t>
+    <t xml:space="preserve">Conventions: "Static actuals" never change once filed (restated only if the company restates). Market data carries dual stamps; "Data as of" (the market close the values describe) and "Last refreshed" (when the file was last updated). Analyst assumptions are the author's judgment; the Version History tab is the audit trail.</t>
   </si>
 </sst>
 </file>
@@ -2021,7 +2030,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -2374,20 +2383,20 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="str">
-        <f aca="false">HYPERLINK("Finance_AI_Dashboard.html","▸  Interactive dashboard  —  toggle industry, scenario and region in your browser (same folder)")</f>
-        <v>▸  Interactive dashboard  —  toggle industry, scenario and region in your browser (same folder)</v>
+        <f aca="false">HYPERLINK("Finance_AI_Dashboard.html","▸  Interactive dashboard  ·  toggle industry, scenario and region in your browser (same folder)")</f>
+        <v>▸  Interactive dashboard  ·  toggle industry, scenario and region in your browser (same folder)</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="str">
-        <f aca="false">HYPERLINK("README.md","▸  Portfolio README  —  overview of all three models and how they fit together")</f>
-        <v>▸  Portfolio README  —  overview of all three models and how they fit together</v>
+        <f aca="false">HYPERLINK("README.md","▸  Portfolio README  ·  overview of all three models and how they fit together")</f>
+        <v>▸  Portfolio README  ·  overview of all three models and how they fit together</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="str">
-        <f aca="false">HYPERLINK("refresh_market_data.py","▸  Market-data refresh script  —  run to update prices, rates and refresh stamps everywhere")</f>
-        <v>▸  Market-data refresh script  —  run to update prices, rates and refresh stamps everywhere</v>
+        <f aca="false">HYPERLINK("refresh_market_data.py","▸  Market-data refresh script  ·  run to update prices, rates and refresh stamps everywhere")</f>
+        <v>▸  Market-data refresh script  ·  run to update prices, rates and refresh stamps everywhere</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2397,68 +2406,68 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Assumptions'!A1","▸  Assumptions  —  Margin, tax, working-capital and financing drivers")</f>
-        <v>▸  Assumptions  —  Margin, tax, working-capital and financing drivers</v>
+        <f aca="false">HYPERLINK("#'Assumptions'!A1","▸  Assumptions  ·  Margin, tax, working-capital and financing drivers")</f>
+        <v>▸  Assumptions  ·  Margin, tax, working-capital and financing drivers</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Revenue Drivers'!A1","▸  Revenue Drivers  —  Bottoms-up sector build driving revenue and key costs")</f>
-        <v>▸  Revenue Drivers  —  Bottoms-up sector build driving revenue and key costs</v>
+        <f aca="false">HYPERLINK("#'Revenue Drivers'!A1","▸  Revenue Drivers  ·  Bottoms-up sector build driving revenue and key costs")</f>
+        <v>▸  Revenue Drivers  ·  Bottoms-up sector build driving revenue and key costs</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Regional Breakdown'!A1","▸  Regional Breakdown  —  NA / Europe / APAC splits and the Standard / Best / Low case selector")</f>
-        <v>▸  Regional Breakdown  —  NA / Europe / APAC splits and the Standard / Best / Low case selector</v>
+        <f aca="false">HYPERLINK("#'Regional Breakdown'!A1","▸  Regional Breakdown  ·  NA / Europe / APAC splits and the Standard / Best / Low case selector")</f>
+        <v>▸  Regional Breakdown  ·  NA / Europe / APAC splits and the Standard / Best / Low case selector</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Income Statement'!A1","▸  Income Statement  —  Revenue build-down to EPS")</f>
-        <v>▸  Income Statement  —  Revenue build-down to EPS</v>
+        <f aca="false">HYPERLINK("#'Income Statement'!A1","▸  Income Statement  ·  Revenue build-down to EPS")</f>
+        <v>▸  Income Statement  ·  Revenue build-down to EPS</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Balance Sheet'!A1","▸  Balance Sheet  —  Assets, liabilities and equity, with balance check")</f>
-        <v>▸  Balance Sheet  —  Assets, liabilities and equity, with balance check</v>
+        <f aca="false">HYPERLINK("#'Balance Sheet'!A1","▸  Balance Sheet  ·  Assets, liabilities and equity, with balance check")</f>
+        <v>▸  Balance Sheet  ·  Assets, liabilities and equity, with balance check</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Cash Flow'!A1","▸  Cash Flow  —  Indirect-method cash flow; ending cash links to the balance sheet")</f>
-        <v>▸  Cash Flow  —  Indirect-method cash flow; ending cash links to the balance sheet</v>
+        <f aca="false">HYPERLINK("#'Cash Flow'!A1","▸  Cash Flow  ·  Indirect-method cash flow; ending cash links to the balance sheet")</f>
+        <v>▸  Cash Flow  ·  Indirect-method cash flow; ending cash links to the balance sheet</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Budget vs Actual'!A1","▸  Budget vs Actual  —  FY2025 vs guidance with automatic &gt;10% variance flagging")</f>
-        <v>▸  Budget vs Actual  —  FY2025 vs guidance with automatic &gt;10% variance flagging</v>
+        <f aca="false">HYPERLINK("#'Budget vs Actual'!A1","▸  Budget vs Actual  ·  FY2025 vs guidance with automatic &gt;10% variance flagging")</f>
+        <v>▸  Budget vs Actual  ·  FY2025 vs guidance with automatic &gt;10% variance flagging</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Market Inputs'!A1","▸  Market Inputs  —  Rates and valuation multiples with refresh stamps")</f>
-        <v>▸  Market Inputs  —  Rates and valuation multiples with refresh stamps</v>
+        <f aca="false">HYPERLINK("#'Market Inputs'!A1","▸  Market Inputs  ·  Rates and valuation multiples with refresh stamps")</f>
+        <v>▸  Market Inputs  ·  Rates and valuation multiples with refresh stamps</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Competitor Benchmarking'!A1","▸  Competitor Benchmarking  —  Two public comps + peer median + industry benchmarks")</f>
-        <v>▸  Competitor Benchmarking  —  Two public comps + peer median + industry benchmarks</v>
+        <f aca="false">HYPERLINK("#'Competitor Benchmarking'!A1","▸  Competitor Benchmarking  ·  Two public comps + peer median + industry benchmarks")</f>
+        <v>▸  Competitor Benchmarking  ·  Two public comps + peer median + industry benchmarks</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Version History'!A1","▸  Version History  —  Audit log of every assumptions and data refresh")</f>
-        <v>▸  Version History  —  Audit log of every assumptions and data refresh</v>
+        <f aca="false">HYPERLINK("#'Version History'!A1","▸  Version History  ·  Audit log of every assumptions and data refresh")</f>
+        <v>▸  Version History  ·  Audit log of every assumptions and data refresh</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="str">
-        <f aca="false">HYPERLINK("#'Sources'!A1","▸  Sources  —  Where every input comes from — citations, links, last-updated dates")</f>
-        <v>▸  Sources  —  Where every input comes from — citations, links, last-updated dates</v>
+        <f aca="false">HYPERLINK("#'Sources'!A1","▸  Sources  ·  Where every input comes from: citations, links, last-updated dates")</f>
+        <v>▸  Sources  ·  Where every input comes from: citations, links, last-updated dates</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3068,16 +3077,26 @@
         <v>414</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="70"/>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="67" t="s">
+        <v>415</v>
+      </c>
+      <c r="B14" s="67" t="s">
+        <v>391</v>
+      </c>
+      <c r="C14" s="67" t="s">
+        <v>387</v>
+      </c>
+      <c r="D14" s="70" t="s">
+        <v>416</v>
+      </c>
+      <c r="E14" s="70" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -3110,37 +3129,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="71" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B4" s="71" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C4" s="71" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D4" s="71" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E4" s="71" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F4" s="71" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="72" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B5" s="73"/>
       <c r="C5" s="73"/>
@@ -3150,13 +3169,13 @@
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="68" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B6" s="68" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D6" s="74" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1404655/000119312526046563/hubs-ex99_1.htm","Open ↗")</f>
@@ -3166,18 +3185,18 @@
         <v>386</v>
       </c>
       <c r="F6" s="75" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="68" t="s">
+        <v>432</v>
+      </c>
+      <c r="B7" s="68" t="s">
         <v>429</v>
       </c>
-      <c r="B7" s="68" t="s">
-        <v>426</v>
-      </c>
       <c r="C7" s="68" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D7" s="74" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1404655/000095017025018839/hubs-ex99_1.htm","Open ↗")</f>
@@ -3187,18 +3206,18 @@
         <v>386</v>
       </c>
       <c r="F7" s="75" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="68" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B8" s="68" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C8" s="68" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D8" s="74" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1404655/000119312526046646/R76.htm","Open ↗")</f>
@@ -3208,18 +3227,18 @@
         <v>391</v>
       </c>
       <c r="F8" s="75" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="68" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B9" s="68" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C9" s="68" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="D9" s="74" t="str">
         <f aca="false">HYPERLINK("https://ir.hubspot.com/news-releases/news-release-details/hubspot-reports-q4-and-full-year-2023-results","Open ↗")</f>
@@ -3229,12 +3248,12 @@
         <v>391</v>
       </c>
       <c r="F9" s="75" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="72" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B10" s="73"/>
       <c r="C10" s="73"/>
@@ -3244,13 +3263,13 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="68" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B11" s="68" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C11" s="68" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D11" s="74" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1404655/000095017025018839/hubs-ex99_1.htm","Open ↗")</f>
@@ -3260,12 +3279,12 @@
         <v>391</v>
       </c>
       <c r="F11" s="75" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="72" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B12" s="73"/>
       <c r="C12" s="73"/>
@@ -3275,70 +3294,70 @@
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="68" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B13" s="68" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C13" s="68" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D13" s="74" t="str">
         <f aca="false">HYPERLINK("https://home.treasury.gov/resource-center/data-chart-center/interest-rates/","Open ↗")</f>
         <v>Open ↗</v>
       </c>
       <c r="E13" s="68" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F13" s="75" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="68" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B14" s="68" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C14" s="68" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D14" s="74" t="str">
         <f aca="false">HYPERLINK("https://www.newyorkfed.org/markets/reference-rates/sofr","Open ↗")</f>
         <v>Open ↗</v>
       </c>
       <c r="E14" s="68" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F14" s="75" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="68" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B15" s="68" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C15" s="68" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="D15" s="74" t="str">
         <f aca="false">HYPERLINK("https://stockanalysis.com/stocks/hubs/statistics/","Open ↗")</f>
         <v>Open ↗</v>
       </c>
       <c r="E15" s="68" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F15" s="75" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="72" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B16" s="73"/>
       <c r="C16" s="73"/>
@@ -3348,13 +3367,13 @@
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="68" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B17" s="68" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C17" s="68" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D17" s="74" t="str">
         <f aca="false">HYPERLINK("https://www.salesforce.com/news/press-releases/2026/02/25/fy26-q4-earnings/","Open ↗")</f>
@@ -3364,18 +3383,18 @@
         <v>391</v>
       </c>
       <c r="F17" s="75" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="68" t="s">
+        <v>466</v>
+      </c>
+      <c r="B18" s="68" t="s">
         <v>463</v>
       </c>
-      <c r="B18" s="68" t="s">
-        <v>460</v>
-      </c>
       <c r="C18" s="68" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="D18" s="74" t="str">
         <f aca="false">HYPERLINK("https://www.sec.gov/Archives/edgar/data/1845338/000117891326000346/exhibit_99-1.htm","Open ↗")</f>
@@ -3385,33 +3404,33 @@
         <v>391</v>
       </c>
       <c r="F18" s="75" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="68" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B19" s="68" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C19" s="68" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D19" s="74" t="str">
         <f aca="false">HYPERLINK("https://cloudedjudgement.substack.com/p/clouded-judgement-71026-own-your","Open ↗")</f>
         <v>Open ↗</v>
       </c>
       <c r="E19" s="68" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F19" s="75" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="72" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B20" s="73"/>
       <c r="C20" s="73"/>
@@ -3421,13 +3440,13 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="68" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B21" s="68" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C21" s="68" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D21" s="76" t="s">
         <v>350</v>
@@ -3436,12 +3455,12 @@
         <v>391</v>
       </c>
       <c r="F21" s="75" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
